--- a/Excel Model/DCF_model.xlsx
+++ b/Excel Model/DCF_model.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vandanbhalala/Pycharm Projects/Projects/Investment Banking Projects/Project 1/Excel Model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8F886C7-8F07-9949-BA6D-B241F985FF9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{566655EB-E15F-A243-A70D-4289ED26C21A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="580" windowWidth="28800" windowHeight="18060" xr2:uid="{B88EEFB7-8CE1-9849-9981-D3115FCF35A8}"/>
+    <workbookView xWindow="0" yWindow="580" windowWidth="28800" windowHeight="18060" activeTab="2" xr2:uid="{B88EEFB7-8CE1-9849-9981-D3115FCF35A8}"/>
   </bookViews>
   <sheets>
     <sheet name="Assumptions" sheetId="1" r:id="rId1"/>
@@ -191,7 +191,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="7">
+  <numFmts count="8">
     <numFmt numFmtId="5" formatCode="&quot;$&quot;#,##0_);\(&quot;$&quot;#,##0\)"/>
     <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
     <numFmt numFmtId="7" formatCode="&quot;$&quot;#,##0.00_);\(&quot;$&quot;#,##0.00\)"/>
@@ -199,6 +199,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00_);\(&quot;$&quot;#,##0.000\)"/>
   </numFmts>
   <fonts count="14" x14ac:knownFonts="1">
     <font>
@@ -372,7 +373,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -424,6 +425,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -868,7 +872,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" ht="14" x14ac:dyDescent="0.15">
       <c r="A8" s="3" t="s">
         <v>6</v>
       </c>
@@ -882,18 +886,18 @@
       <c r="E8" s="30">
         <v>55</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="40">
         <f t="dataTable" ref="F8:H12" dt2D="1" dtr="1" r1="B31" r2="B2"/>
         <v>86.470296961573808</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G8" s="40">
         <v>-265.53605668090319</v>
       </c>
-      <c r="H8" s="6">
+      <c r="H8" s="40">
         <v>-584.70427754079969</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" ht="14" x14ac:dyDescent="0.15">
       <c r="A9" s="3" t="s">
         <v>7</v>
       </c>
@@ -907,17 +911,17 @@
       <c r="E9" s="30">
         <v>65</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="40">
         <v>1754.5935427573766</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G9" s="40">
         <v>1299.9432146007639</v>
       </c>
-      <c r="H9" s="6">
+      <c r="H9" s="40">
         <v>887.70651816175973</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="14" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" ht="14" x14ac:dyDescent="0.15">
       <c r="A10" s="3" t="s">
         <v>8</v>
       </c>
@@ -931,47 +935,47 @@
       <c r="E10" s="30">
         <v>76.760000000000005</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="40">
         <v>3716.3064798132395</v>
       </c>
-      <c r="G10" s="6">
+      <c r="G10" s="40">
         <v>3140.9468376280029</v>
       </c>
-      <c r="H10" s="6">
+      <c r="H10" s="40">
         <v>2619.2616139079696</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="14" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" ht="14" x14ac:dyDescent="0.15">
       <c r="A11" s="3"/>
       <c r="B11" s="34"/>
       <c r="C11" s="7"/>
       <c r="E11" s="30">
         <v>85</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F11" s="40">
         <v>5090.8400343489775</v>
       </c>
-      <c r="G11" s="6">
+      <c r="G11" s="40">
         <v>4430.9017571640961</v>
       </c>
-      <c r="H11" s="6">
+      <c r="H11" s="40">
         <v>3832.5281095668779</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="14" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" ht="14" x14ac:dyDescent="0.15">
       <c r="A12" s="3"/>
       <c r="B12" s="34"/>
       <c r="C12" s="8"/>
       <c r="E12" s="30">
         <v>95</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F12" s="40">
         <v>6758.9632801447797</v>
       </c>
-      <c r="G12" s="6">
+      <c r="G12" s="40">
         <v>5996.3810284457604</v>
       </c>
-      <c r="H12" s="6">
+      <c r="H12" s="40">
         <v>5304.9389052694369</v>
       </c>
     </row>

--- a/Excel Model/DCF_model.xlsx
+++ b/Excel Model/DCF_model.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vandanbhalala/Pycharm Projects/Projects/Investment Banking Projects/Project 1/Excel Model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F3CF148-E971-4B40-8164-F679BAB19668}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8F26A56-D927-784C-A61B-BC5ECCCC507D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="580" windowWidth="28800" windowHeight="18060" xr2:uid="{B88EEFB7-8CE1-9849-9981-D3115FCF35A8}"/>
   </bookViews>
@@ -79,9 +79,6 @@
     <t>Gas gathering, processing and transportation expenses</t>
   </si>
   <si>
-    <t>General and administrative (excluding LTIP and transaction costs)</t>
-  </si>
-  <si>
     <t>Capital</t>
   </si>
   <si>
@@ -136,9 +133,6 @@
     <t>CAPEX ($)</t>
   </si>
   <si>
-    <t>Free Cash Flow ($)</t>
-  </si>
-  <si>
     <t>PV  ($)</t>
   </si>
   <si>
@@ -149,9 +143,6 @@
   </si>
   <si>
     <t>BOE / month</t>
-  </si>
-  <si>
-    <t>Free Cash Flow ($MM)</t>
   </si>
   <si>
     <t>EBITDA ($)</t>
@@ -171,6 +162,15 @@
   <si>
     <t>Product Mix (%)</t>
   </si>
+  <si>
+    <t>General and administrative (excluding LTIP and transaction costs)</t>
+  </si>
+  <si>
+    <t>Net Operating Cash Flow ($)</t>
+  </si>
+  <si>
+    <t>Net Operating Cash Flow ($MM)</t>
+  </si>
 </sst>
 </file>
 
@@ -185,7 +185,7 @@
     <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00_);\(&quot;$&quot;#,##0.000\)"/>
     <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00_);&quot;$&quot;#,##0.000"/>
-    <numFmt numFmtId="171" formatCode="&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
   <fonts count="12" x14ac:knownFonts="1">
     <font>
@@ -442,7 +442,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -468,17 +468,10 @@
     <xf numFmtId="3" fontId="9" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="5" fontId="9" fillId="2" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="5" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="7" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -496,7 +489,7 @@
     <xf numFmtId="166" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="7" fontId="6" fillId="0" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -505,13 +498,6 @@
     <xf numFmtId="7" fontId="6" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -524,18 +510,27 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="7" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="4" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -892,73 +887,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="40"/>
+      <c r="B1" s="1"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="46">
+      <c r="B2" s="40">
         <v>76.760000000000005</v>
       </c>
-      <c r="C2" s="47"/>
-      <c r="F2" s="27" t="s">
+      <c r="C2" s="41"/>
+      <c r="F2" s="49" t="s">
+        <v>36</v>
+      </c>
+      <c r="G2" s="49"/>
+      <c r="H2" s="49"/>
+      <c r="I2" s="49"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="40">
+        <v>13.66</v>
+      </c>
+      <c r="C3" s="41"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="40">
+        <v>0.85</v>
+      </c>
+      <c r="C4" s="41"/>
+      <c r="F4" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="G4" s="32"/>
+      <c r="H4" s="32"/>
+      <c r="I4" s="32"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A5" s="1"/>
+      <c r="B5" s="42"/>
+      <c r="C5" s="41"/>
+    </row>
+    <row r="6" spans="1:9" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="1"/>
+      <c r="B6" s="42"/>
+      <c r="C6" s="43"/>
+      <c r="G6" s="50" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" s="50"/>
+      <c r="I6" s="50"/>
+    </row>
+    <row r="7" spans="1:9" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
-      <c r="I2" s="27"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A3" s="48" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="46">
-        <v>13.66</v>
-      </c>
-      <c r="C3" s="47"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A4" s="48" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="46">
-        <v>0.85</v>
-      </c>
-      <c r="C4" s="47"/>
-      <c r="F4" s="35" t="s">
-        <v>40</v>
-      </c>
-      <c r="G4" s="35"/>
-      <c r="H4" s="35"/>
-      <c r="I4" s="35"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A5" s="48"/>
-      <c r="B5" s="49"/>
-      <c r="C5" s="47"/>
-    </row>
-    <row r="6" spans="1:9" ht="14" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="48"/>
-      <c r="B6" s="49"/>
-      <c r="C6" s="50"/>
-      <c r="G6" s="38" t="s">
-        <v>27</v>
-      </c>
-      <c r="H6" s="38"/>
-      <c r="I6" s="38"/>
-    </row>
-    <row r="7" spans="1:9" ht="14" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="B7" s="49"/>
-      <c r="C7" s="50"/>
-      <c r="E7" s="45"/>
+      <c r="B7" s="42"/>
+      <c r="C7" s="43"/>
+      <c r="E7" s="39"/>
       <c r="F7" s="5">
         <f>'Annual Summary'!H18</f>
         <v>3140.9468376280029</v>
@@ -974,40 +968,40 @@
       </c>
     </row>
     <row r="8" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="48" t="s">
+      <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="52">
+      <c r="B8" s="45">
         <v>0.46</v>
       </c>
-      <c r="C8" s="47"/>
-      <c r="E8" s="39" t="s">
-        <v>41</v>
-      </c>
-      <c r="F8" s="36">
+      <c r="C8" s="41"/>
+      <c r="E8" s="48" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8" s="33">
         <v>55</v>
       </c>
-      <c r="G8" s="31">
+      <c r="G8" s="28">
         <f t="dataTable" ref="G8:I12" dt2D="1" dtr="1" r1="B31" r2="B2"/>
         <v>86.470296961573808</v>
       </c>
-      <c r="H8" s="41">
+      <c r="H8" s="35">
         <v>-265.53605668090319</v>
       </c>
-      <c r="I8" s="42">
+      <c r="I8" s="36">
         <v>-584.70427754079969</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="14" x14ac:dyDescent="0.15">
-      <c r="A9" s="48" t="s">
+      <c r="A9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="52">
+      <c r="B9" s="45">
         <v>0.27</v>
       </c>
-      <c r="C9" s="47"/>
-      <c r="E9" s="39"/>
-      <c r="F9" s="36">
+      <c r="C9" s="41"/>
+      <c r="E9" s="48"/>
+      <c r="F9" s="33">
         <v>65</v>
       </c>
       <c r="G9" s="25">
@@ -1016,20 +1010,20 @@
       <c r="H9" s="25">
         <v>1299.9432146007639</v>
       </c>
-      <c r="I9" s="32">
+      <c r="I9" s="29">
         <v>887.70651816175973</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="14" x14ac:dyDescent="0.15">
-      <c r="A10" s="48" t="s">
+      <c r="A10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="52">
+      <c r="B10" s="45">
         <v>0.27</v>
       </c>
-      <c r="C10" s="47"/>
-      <c r="E10" s="39"/>
-      <c r="F10" s="36">
+      <c r="C10" s="41"/>
+      <c r="E10" s="48"/>
+      <c r="F10" s="33">
         <v>76.760000000000005</v>
       </c>
       <c r="G10" s="25">
@@ -1038,16 +1032,16 @@
       <c r="H10" s="25">
         <v>3140.9468376280029</v>
       </c>
-      <c r="I10" s="32">
+      <c r="I10" s="29">
         <v>2619.2616139079696</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="14" x14ac:dyDescent="0.15">
-      <c r="A11" s="48"/>
-      <c r="B11" s="49"/>
-      <c r="C11" s="47"/>
-      <c r="E11" s="39"/>
-      <c r="F11" s="36">
+      <c r="A11" s="1"/>
+      <c r="B11" s="42"/>
+      <c r="C11" s="41"/>
+      <c r="E11" s="48"/>
+      <c r="F11" s="33">
         <v>85</v>
       </c>
       <c r="G11" s="25">
@@ -1056,196 +1050,192 @@
       <c r="H11" s="25">
         <v>4430.9017571640961</v>
       </c>
-      <c r="I11" s="32">
+      <c r="I11" s="29">
         <v>3832.5281095668779</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="14" x14ac:dyDescent="0.15">
-      <c r="A12" s="48"/>
-      <c r="B12" s="49"/>
-      <c r="C12" s="50"/>
-      <c r="E12" s="39"/>
-      <c r="F12" s="37">
+      <c r="A12" s="1"/>
+      <c r="B12" s="42"/>
+      <c r="C12" s="43"/>
+      <c r="E12" s="48"/>
+      <c r="F12" s="34">
         <v>95</v>
       </c>
-      <c r="G12" s="33">
+      <c r="G12" s="30">
         <v>6758.9632801447797</v>
       </c>
-      <c r="H12" s="33">
+      <c r="H12" s="30">
         <v>5996.3810284457604</v>
       </c>
-      <c r="I12" s="34">
+      <c r="I12" s="31">
         <v>5304.9389052694369</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A13" s="51" t="s">
+      <c r="A13" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="B13" s="49"/>
-      <c r="C13" s="50"/>
+      <c r="B13" s="42"/>
+      <c r="C13" s="43"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A14" s="48" t="s">
+      <c r="A14" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="46">
+      <c r="B14" s="40">
         <v>9.15</v>
       </c>
-      <c r="C14" s="47"/>
+      <c r="C14" s="41"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A15" s="48" t="s">
+      <c r="A15" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="46">
+      <c r="B15" s="40">
         <v>2.41</v>
       </c>
-      <c r="C15" s="47"/>
+      <c r="C15" s="41"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A16" s="48" t="s">
+      <c r="A16" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B16" s="46">
+      <c r="B16" s="40">
         <v>0.92</v>
       </c>
-      <c r="C16" s="47"/>
+      <c r="C16" s="41"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A17" s="48" t="s">
+      <c r="A17" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B17" s="46">
+      <c r="B17" s="40">
         <v>0.36</v>
       </c>
-      <c r="C17" s="47"/>
-    </row>
-    <row r="18" spans="1:9" ht="14" x14ac:dyDescent="0.2">
-      <c r="A18" s="48" t="s">
-        <v>12</v>
-      </c>
-      <c r="B18" s="46">
+      <c r="C17" s="41"/>
+    </row>
+    <row r="18" spans="1:9" ht="14" x14ac:dyDescent="0.15">
+      <c r="A18" s="51" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="40">
         <v>1.75</v>
       </c>
-      <c r="C18" s="47"/>
-      <c r="F18" s="28"/>
-      <c r="G18" s="29"/>
-      <c r="H18" s="29"/>
-      <c r="I18" s="29"/>
+      <c r="C18" s="41"/>
+      <c r="F18" s="27"/>
+      <c r="G18" s="25"/>
+      <c r="H18" s="25"/>
+      <c r="I18" s="25"/>
     </row>
     <row r="19" spans="1:9" ht="14" x14ac:dyDescent="0.15">
-      <c r="A19" s="48"/>
-      <c r="B19" s="49"/>
-      <c r="C19" s="47"/>
-      <c r="F19" s="30"/>
+      <c r="A19" s="51"/>
+      <c r="B19" s="40"/>
+      <c r="C19" s="41"/>
+      <c r="F19" s="27"/>
       <c r="G19" s="25"/>
       <c r="H19" s="25"/>
       <c r="I19" s="25"/>
     </row>
     <row r="20" spans="1:9" ht="14" x14ac:dyDescent="0.15">
-      <c r="A20" s="48"/>
-      <c r="B20" s="49"/>
-      <c r="C20" s="47"/>
-      <c r="F20" s="30"/>
+      <c r="A20" s="1"/>
+      <c r="B20" s="42"/>
+      <c r="C20" s="41"/>
+      <c r="F20" s="27"/>
       <c r="G20" s="25"/>
       <c r="H20" s="25"/>
       <c r="I20" s="25"/>
     </row>
     <row r="21" spans="1:9" ht="14" x14ac:dyDescent="0.15">
-      <c r="A21" s="51" t="s">
-        <v>13</v>
-      </c>
-      <c r="B21" s="49"/>
-      <c r="C21" s="50"/>
-      <c r="F21" s="30"/>
+      <c r="A21" s="44" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" s="42"/>
+      <c r="C21" s="43"/>
+      <c r="F21" s="27"/>
       <c r="G21" s="25"/>
       <c r="H21" s="25"/>
       <c r="I21" s="25"/>
     </row>
     <row r="22" spans="1:9" ht="14" x14ac:dyDescent="0.15">
-      <c r="A22" s="48" t="s">
-        <v>14</v>
-      </c>
-      <c r="B22" s="49">
+      <c r="A22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B22" s="42">
         <v>1.53</v>
       </c>
-      <c r="C22" s="50"/>
-      <c r="F22" s="30"/>
+      <c r="C22" s="43"/>
+      <c r="F22" s="27"/>
       <c r="G22" s="25"/>
       <c r="H22" s="25"/>
       <c r="I22" s="25"/>
     </row>
     <row r="23" spans="1:9" ht="14" x14ac:dyDescent="0.15">
-      <c r="A23" s="48" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23" s="54">
+      <c r="A23" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" s="47">
         <v>47600000</v>
       </c>
-      <c r="C23" s="50"/>
-      <c r="F23" s="30"/>
+      <c r="C23" s="43"/>
+      <c r="F23" s="27"/>
       <c r="G23" s="25"/>
       <c r="H23" s="25"/>
       <c r="I23" s="25"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A24" s="48" t="s">
+      <c r="A24" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" s="42">
+        <v>120</v>
+      </c>
+      <c r="C24" s="43"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A25" s="1"/>
+      <c r="B25" s="42"/>
+      <c r="C25" s="43"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A26" s="1"/>
+      <c r="B26" s="42"/>
+      <c r="C26" s="43"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A27" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="B24" s="49">
-        <v>120</v>
-      </c>
-      <c r="C24" s="50"/>
-      <c r="F24" s="40"/>
-      <c r="G24" s="40"/>
-      <c r="H24" s="40"/>
-      <c r="I24" s="40"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A25" s="48"/>
-      <c r="B25" s="49"/>
-      <c r="C25" s="50"/>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A26" s="48"/>
-      <c r="B26" s="49"/>
-      <c r="C26" s="50"/>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A27" s="51" t="s">
+      <c r="B27" s="42"/>
+      <c r="C27" s="43"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A28" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B27" s="49"/>
-      <c r="C27" s="50"/>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A28" s="48" t="s">
-        <v>18</v>
-      </c>
-      <c r="B28" s="52">
+      <c r="B28" s="45">
         <v>0.1</v>
       </c>
-      <c r="C28" s="50"/>
+      <c r="C28" s="43"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A29" s="48"/>
-      <c r="B29" s="49"/>
-      <c r="C29" s="50"/>
+      <c r="A29" s="1"/>
+      <c r="B29" s="42"/>
+      <c r="C29" s="43"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A30" s="48"/>
-      <c r="B30" s="49"/>
-      <c r="C30" s="50"/>
+      <c r="A30" s="1"/>
+      <c r="B30" s="42"/>
+      <c r="C30" s="43"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A31" s="48" t="s">
-        <v>27</v>
-      </c>
-      <c r="B31" s="53">
+      <c r="A31" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B31" s="46">
         <v>1</v>
       </c>
-      <c r="C31" s="50"/>
+      <c r="C31" s="43"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A32" s="1"/>
@@ -1866,7 +1856,7 @@
     <mergeCell ref="G6:I6"/>
   </mergeCells>
   <conditionalFormatting sqref="G8:I12">
-    <cfRule type="colorScale" priority="2">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -1875,8 +1865,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G19:I23">
-    <cfRule type="colorScale" priority="1">
+  <conditionalFormatting sqref="G18:I23">
+    <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -1902,7 +1892,7 @@
     <col min="6" max="6" width="17.33203125" style="4" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.33203125" style="4" customWidth="1"/>
     <col min="8" max="8" width="17.33203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="24.1640625" style="4" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="19" style="4" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.83203125" style="4"/>
     <col min="12" max="12" width="18.6640625" style="4" bestFit="1" customWidth="1"/>
@@ -1910,35 +1900,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="43" t="s">
-        <v>19</v>
-      </c>
-      <c r="B1" s="43" t="s">
+      <c r="A1" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="37" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="37" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="43" t="s">
+      <c r="E1" s="37" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="37" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="D1" s="43" t="s">
-        <v>35</v>
-      </c>
-      <c r="E1" s="43" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1" s="43" t="s">
+      <c r="H1" s="37" t="s">
         <v>29</v>
       </c>
-      <c r="G1" s="43" t="s">
-        <v>37</v>
-      </c>
-      <c r="H1" s="43" t="s">
+      <c r="I1" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="J1" s="37" t="s">
         <v>30</v>
-      </c>
-      <c r="I1" s="43" t="s">
-        <v>31</v>
-      </c>
-      <c r="J1" s="43" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="14" x14ac:dyDescent="0.2">
@@ -8933,7 +8923,7 @@
         <v>0</v>
       </c>
       <c r="I176" s="10">
-        <f>E176-F176-H176</f>
+        <f t="shared" si="8"/>
         <v>41528449.760851085</v>
       </c>
       <c r="J176" s="10">
@@ -9154,7 +9144,7 @@
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A183" s="21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B183" s="22">
         <f t="shared" ref="B183:H183" si="9">SUM(B2:B181)</f>
@@ -9209,35 +9199,35 @@
     <col min="4" max="4" width="11.1640625" style="4" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.5" style="4" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.1640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="26" style="4" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="8.6640625" style="4" bestFit="1" customWidth="1"/>
     <col min="9" max="16384" width="10.83203125" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="38" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="44" t="s">
+      <c r="C1" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="44" t="s">
+      <c r="D1" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="44" t="s">
+      <c r="E1" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="44" t="s">
-        <v>38</v>
-      </c>
-      <c r="F1" s="44" t="s">
+      <c r="G1" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="H1" s="38" t="s">
         <v>24</v>
-      </c>
-      <c r="G1" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="H1" s="44" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.15">
@@ -9747,7 +9737,7 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A18" s="18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B18" s="19">
         <f>SUM(B2:B16)</f>
